--- a/teams-and-rosters/CS320-Sp25-102-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-102-roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FB2113-5DBA-474D-8277-3B2C4576BF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFD0ECB-1AF4-4D54-AD69-511DF160EE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1935" windowWidth="21480" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1410" yWindow="1410" windowWidth="11490" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-102-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>Major</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>Thomas</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Tucker</t>
   </si>
 </sst>
 </file>
@@ -479,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -650,51 +656,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -783,7 +744,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -804,21 +765,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1189,228 +1142,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="A4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>8</v>
+        <v>19</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="15"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="12"/>
+    </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D26" s="3"/>
     </row>

--- a/teams-and-rosters/CS320-Sp25-102-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-102-roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFD0ECB-1AF4-4D54-AD69-511DF160EE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5255D-9E34-4690-A305-8EBF35327913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1410" windowWidth="11490" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="1050" windowWidth="12720" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-102-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
   <si>
     <t>Major</t>
   </si>
@@ -37,9 +37,6 @@
     <t>CS320 Section 102: M-W-F  3:00p to 3:50p</t>
   </si>
   <si>
-    <t>Campbell</t>
-  </si>
-  <si>
     <t>Aidan</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>William</t>
   </si>
   <si>
-    <t>CyberMgt</t>
-  </si>
-  <si>
     <t>SR</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Jackson</t>
   </si>
   <si>
-    <t>ME</t>
-  </si>
-  <si>
     <t>Hornbeck</t>
   </si>
   <si>
@@ -88,12 +79,6 @@
     <t>Jeremiah</t>
   </si>
   <si>
-    <t>Natale</t>
-  </si>
-  <si>
-    <t>Evan</t>
-  </si>
-  <si>
     <t>JR</t>
   </si>
   <si>
@@ -140,6 +125,15 @@
   </si>
   <si>
     <t>Tucker</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Caroline</t>
+  </si>
+  <si>
+    <t>CybMgt</t>
   </si>
 </sst>
 </file>
@@ -1165,44 +1159,44 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>7</v>
-      </c>
       <c r="D3" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1213,38 +1207,38 @@
         <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="D7" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,24 +1249,24 @@
         <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>7</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,81 +1277,73 @@
         <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="C12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>7</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="C14" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>24</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>

--- a/teams-and-rosters/CS320-Sp25-102-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-102-roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5255D-9E34-4690-A305-8EBF35327913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B946B-E927-4F63-8B7A-57090B62F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="1050" windowWidth="12720" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="615" windowWidth="22050" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-102-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>Onyejesi</t>
   </si>
   <si>
-    <t>Chibudom</t>
-  </si>
-  <si>
     <t>Reppert</t>
   </si>
   <si>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>CybMgt</t>
+  </si>
+  <si>
+    <t>Ethan</t>
   </si>
 </sst>
 </file>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>6</v>
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>16</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>6</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>22</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>6</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>22</v>
